--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5768AC1C-723C-4607-B6EB-C72EC8542A72}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5530CB9A-AC36-4CC2-92DD-6069CA72705B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -62,9 +63,6 @@
     <t>TRANSFER TOTAL METALIC FILM SILVER QT-001A - AMERICA ASIA</t>
   </si>
   <si>
-    <t>TRANSFER TOTAL METALIC FILM GRAFITE QT-339A - AMERICA ASIA</t>
-  </si>
-  <si>
     <t>DOTS FILM LASER - AMERICA ASIA</t>
   </si>
   <si>
@@ -105,6 +103,12 @@
   </si>
   <si>
     <t>PROTECTION FILM 35UM - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>28/0/2026</t>
+  </si>
+  <si>
+    <t>TRANSFER TOTAL METALIC FILM PEWTER QT-110A - AMERICA ASIA</t>
   </si>
 </sst>
 </file>
@@ -130,7 +134,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -140,12 +144,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -187,14 +185,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,18 +566,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1255</v>
+        <v>1467</v>
       </c>
       <c r="B2" s="3">
         <v>162</v>
@@ -585,27 +586,27 @@
         <v>6</v>
       </c>
       <c r="D2" s="4">
-        <v>46156</v>
+        <v>46204</v>
       </c>
       <c r="E2" s="3">
-        <v>7485</v>
+        <v>4413</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="6">
-        <v>6000</v>
+        <v>8</v>
+      </c>
+      <c r="G2" s="7">
+        <v>3000</v>
       </c>
       <c r="H2">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>1350</v>
+        <v>1469</v>
       </c>
       <c r="B3" s="3">
         <v>162</v>
@@ -614,27 +615,27 @@
         <v>6</v>
       </c>
       <c r="D3" s="4">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="E3" s="3">
-        <v>7425</v>
+        <v>10090</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="6">
-        <v>3330</v>
+        <v>10</v>
+      </c>
+      <c r="G3" s="7">
+        <v>3250</v>
       </c>
       <c r="H3">
         <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="B4" s="3">
         <v>162</v>
@@ -646,24 +647,24 @@
         <v>46204</v>
       </c>
       <c r="E4" s="3">
-        <v>4413</v>
+        <v>12515</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="6">
-        <v>3000</v>
+        <v>11</v>
+      </c>
+      <c r="G4" s="7">
+        <v>6480</v>
       </c>
       <c r="H4">
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1468</v>
+        <v>1487</v>
       </c>
       <c r="B5" s="3">
         <v>162</v>
@@ -672,27 +673,27 @@
         <v>6</v>
       </c>
       <c r="D5" s="4">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="E5" s="3">
-        <v>7484</v>
+        <v>17075</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6">
-        <v>10620</v>
+        <v>12</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4230</v>
       </c>
       <c r="H5">
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>1469</v>
+        <v>1565</v>
       </c>
       <c r="B6" s="3">
         <v>162</v>
@@ -701,27 +702,27 @@
         <v>6</v>
       </c>
       <c r="D6" s="4">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="E6" s="3">
-        <v>10090</v>
+        <v>7484</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="6">
-        <v>3000</v>
+        <v>9</v>
+      </c>
+      <c r="G6" s="7">
+        <v>9000</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>1470</v>
+        <v>1565</v>
       </c>
       <c r="B7" s="3">
         <v>162</v>
@@ -730,27 +731,27 @@
         <v>6</v>
       </c>
       <c r="D7" s="4">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="E7" s="3">
-        <v>12515</v>
+        <v>7485</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6">
+        <v>7</v>
+      </c>
+      <c r="G7" s="7">
         <v>6000</v>
       </c>
       <c r="H7">
         <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>1487</v>
+        <v>1565</v>
       </c>
       <c r="B8" s="3">
         <v>162</v>
@@ -759,22 +760,22 @@
         <v>6</v>
       </c>
       <c r="D8" s="4">
-        <v>46206</v>
+        <v>46225</v>
       </c>
       <c r="E8" s="3">
-        <v>17075</v>
+        <v>10090</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="6">
-        <v>4000</v>
+        <v>10</v>
+      </c>
+      <c r="G8" s="7">
+        <v>3200</v>
       </c>
       <c r="H8">
         <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -791,24 +792,24 @@
         <v>46225</v>
       </c>
       <c r="E9" s="3">
-        <v>7484</v>
+        <v>17076</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6">
-        <v>9000</v>
+        <v>13</v>
+      </c>
+      <c r="G9" s="7">
+        <v>3070</v>
       </c>
       <c r="H9">
         <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>1565</v>
+        <v>1582</v>
       </c>
       <c r="B10" s="3">
         <v>162</v>
@@ -817,27 +818,27 @@
         <v>6</v>
       </c>
       <c r="D10" s="4">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E10" s="3">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
-        <v>6000</v>
+        <v>9</v>
+      </c>
+      <c r="G10" s="7">
+        <v>8800</v>
       </c>
       <c r="H10">
         <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>1565</v>
+        <v>1582</v>
       </c>
       <c r="B11" s="3">
         <v>162</v>
@@ -846,27 +847,27 @@
         <v>6</v>
       </c>
       <c r="D11" s="4">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E11" s="3">
-        <v>10090</v>
+        <v>7485</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="6">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7">
         <v>3000</v>
       </c>
       <c r="H11">
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>1565</v>
+        <v>1582</v>
       </c>
       <c r="B12" s="3">
         <v>162</v>
@@ -875,27 +876,27 @@
         <v>6</v>
       </c>
       <c r="D12" s="4">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="E12" s="3">
-        <v>17076</v>
+        <v>10090</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="6">
-        <v>3000</v>
+        <v>10</v>
+      </c>
+      <c r="G12" s="7">
+        <v>3100</v>
       </c>
       <c r="H12">
         <v>12</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>1582</v>
+        <v>1602</v>
       </c>
       <c r="B13" s="3">
         <v>162</v>
@@ -904,27 +905,27 @@
         <v>6</v>
       </c>
       <c r="D13" s="4">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="E13" s="3">
         <v>7484</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="6">
-        <v>9000</v>
+        <v>9</v>
+      </c>
+      <c r="G13" s="7">
+        <v>10100</v>
       </c>
       <c r="H13">
         <v>12</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>1582</v>
+        <v>1633</v>
       </c>
       <c r="B14" s="3">
         <v>162</v>
@@ -933,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="4">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="E14" s="3">
         <v>7485</v>
@@ -941,19 +942,19 @@
       <c r="F14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="6">
-        <v>3000</v>
+      <c r="G14" s="7">
+        <v>5000</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>1582</v>
+        <v>1487</v>
       </c>
       <c r="B15" s="3">
         <v>162</v>
@@ -962,27 +963,27 @@
         <v>6</v>
       </c>
       <c r="D15" s="4">
-        <v>46233</v>
+        <v>46206</v>
       </c>
       <c r="E15" s="3">
-        <v>10090</v>
+        <v>17075</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="6">
-        <v>3000</v>
+        <v>12</v>
+      </c>
+      <c r="G15" s="7">
+        <v>1340</v>
       </c>
       <c r="H15">
         <v>12</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>1602</v>
+        <v>1468</v>
       </c>
       <c r="B16" s="3">
         <v>162</v>
@@ -991,27 +992,27 @@
         <v>6</v>
       </c>
       <c r="D16" s="4">
-        <v>46239</v>
+        <v>46204</v>
       </c>
       <c r="E16" s="3">
         <v>7484</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6">
+        <v>9</v>
+      </c>
+      <c r="G16" s="7">
         <v>10000</v>
       </c>
       <c r="H16">
         <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>1633</v>
+        <v>1666</v>
       </c>
       <c r="B17" s="3">
         <v>162</v>
@@ -1020,27 +1021,27 @@
         <v>6</v>
       </c>
       <c r="D17" s="4">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="E17" s="3">
-        <v>7485</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="6">
-        <v>5000</v>
+        <v>10090</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="7">
+        <v>3000</v>
       </c>
       <c r="H17">
         <v>12</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>1487</v>
+        <v>1665</v>
       </c>
       <c r="B18" s="3">
         <v>162</v>
@@ -1049,27 +1050,27 @@
         <v>6</v>
       </c>
       <c r="D18" s="4">
-        <v>46206</v>
+        <v>46252</v>
       </c>
       <c r="E18" s="3">
-        <v>17075</v>
+        <v>7484</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1340</v>
+        <v>9</v>
+      </c>
+      <c r="G18" s="7">
+        <v>20000</v>
       </c>
       <c r="H18">
         <v>12</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>1468</v>
+        <v>1665</v>
       </c>
       <c r="B19" s="3">
         <v>162</v>
@@ -1078,27 +1079,27 @@
         <v>6</v>
       </c>
       <c r="D19" s="4">
-        <v>46204</v>
+        <v>46252</v>
       </c>
       <c r="E19" s="3">
-        <v>7484</v>
+        <v>4413</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="6">
-        <v>10000</v>
+        <v>8</v>
+      </c>
+      <c r="G19" s="7">
+        <v>3000</v>
       </c>
       <c r="H19">
         <v>12</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B20" s="3">
         <v>162</v>
@@ -1110,24 +1111,24 @@
         <v>46252</v>
       </c>
       <c r="E20" s="3">
-        <v>10090</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="6">
-        <v>3000</v>
+        <v>30189</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="7">
+        <v>7000</v>
       </c>
       <c r="H20">
         <v>12</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>1665</v>
+        <v>1487</v>
       </c>
       <c r="B21" s="3">
         <v>162</v>
@@ -1136,27 +1137,27 @@
         <v>6</v>
       </c>
       <c r="D21" s="4">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="E21" s="3">
-        <v>7484</v>
+        <v>17075</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="6">
-        <v>20000</v>
+        <v>12</v>
+      </c>
+      <c r="G21" s="7">
+        <v>2000</v>
       </c>
       <c r="H21">
         <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B22" s="3">
         <v>162</v>
@@ -1168,12 +1169,12 @@
         <v>46252</v>
       </c>
       <c r="E22" s="3">
-        <v>4413</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="6">
+        <v>10090</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7">
         <v>3000</v>
       </c>
       <c r="H22">
@@ -1185,7 +1186,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>1668</v>
+        <v>1697</v>
       </c>
       <c r="B23" s="3">
         <v>162</v>
@@ -1193,26 +1194,27 @@
       <c r="C23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="4">
-        <v>46252</v>
+      <c r="D23" t="s">
+        <v>22</v>
       </c>
       <c r="E23" s="3">
-        <v>30189</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="6">
-        <v>7000</v>
+        <v>9000</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1000</v>
       </c>
       <c r="H23">
         <v>12</v>
       </c>
       <c r="I23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5530CB9A-AC36-4CC2-92DD-6069CA72705B}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0E91B54-7ABF-4411-BFAB-BA25568A32F5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -105,19 +105,23 @@
     <t>PROTECTION FILM 35UM - AMERICA ASIA</t>
   </si>
   <si>
-    <t>28/0/2026</t>
-  </si>
-  <si>
     <t>TRANSFER TOTAL METALIC FILM PEWTER QT-110A - AMERICA ASIA</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL COFFEE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - SILVER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[Blue]###,###,###,##0;[Red]\-###,###,###,##0"/>
     <numFmt numFmtId="165" formatCode="[Blue]###,###,###,##0.000;[Red]\-###,###,###,##0.000"/>
+    <numFmt numFmtId="166" formatCode="[Blue]###########0;[Red]\-###########0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -134,7 +138,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,6 +148,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,17 +195,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,16 +545,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -568,10 +581,10 @@
       <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -582,25 +595,25 @@
       <c r="B2" s="3">
         <v>162</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5">
         <v>46204</v>
       </c>
       <c r="E2" s="3">
         <v>4413</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>3000</v>
       </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="7">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -611,25 +624,25 @@
       <c r="B3" s="3">
         <v>162</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5">
         <v>46204</v>
       </c>
       <c r="E3" s="3">
         <v>10090</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>3250</v>
       </c>
-      <c r="H3">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="H3" s="7">
+        <v>12</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -640,25 +653,25 @@
       <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
         <v>46204</v>
       </c>
       <c r="E4" s="3">
         <v>12515</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>6480</v>
       </c>
-      <c r="H4">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="7">
+        <v>12</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>18</v>
       </c>
     </row>
@@ -669,25 +682,25 @@
       <c r="B5" s="3">
         <v>162</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5">
         <v>46206</v>
       </c>
       <c r="E5" s="3">
         <v>17075</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6">
         <v>4230</v>
       </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="H5" s="7">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -698,25 +711,25 @@
       <c r="B6" s="3">
         <v>162</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5">
         <v>46225</v>
       </c>
       <c r="E6" s="3">
         <v>7484</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="7">
-        <v>9000</v>
-      </c>
-      <c r="H6">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="G6" s="6">
+        <v>8800</v>
+      </c>
+      <c r="H6" s="7">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -727,25 +740,25 @@
       <c r="B7" s="3">
         <v>162</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5">
         <v>46225</v>
       </c>
       <c r="E7" s="3">
         <v>7485</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>6000</v>
       </c>
-      <c r="H7">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H7" s="7">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -756,25 +769,25 @@
       <c r="B8" s="3">
         <v>162</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5">
         <v>46225</v>
       </c>
       <c r="E8" s="3">
         <v>10090</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>3200</v>
       </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="H8" s="7">
+        <v>12</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -785,25 +798,25 @@
       <c r="B9" s="3">
         <v>162</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
         <v>46225</v>
       </c>
       <c r="E9" s="3">
         <v>17076</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>3070</v>
       </c>
-      <c r="H9">
-        <v>12</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="7">
+        <v>12</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -814,25 +827,25 @@
       <c r="B10" s="3">
         <v>162</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5">
         <v>46233</v>
       </c>
       <c r="E10" s="3">
         <v>7484</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="7">
-        <v>8800</v>
-      </c>
-      <c r="H10">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="G10" s="6">
+        <v>9000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -843,25 +856,25 @@
       <c r="B11" s="3">
         <v>162</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
         <v>46233</v>
       </c>
       <c r="E11" s="3">
         <v>7485</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>3000</v>
       </c>
-      <c r="H11">
-        <v>12</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="H11" s="7">
+        <v>12</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -872,25 +885,25 @@
       <c r="B12" s="3">
         <v>162</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5">
         <v>46233</v>
       </c>
       <c r="E12" s="3">
         <v>10090</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>3100</v>
       </c>
-      <c r="H12">
-        <v>12</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="7">
+        <v>12</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -901,25 +914,25 @@
       <c r="B13" s="3">
         <v>162</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
         <v>46239</v>
       </c>
       <c r="E13" s="3">
         <v>7484</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="7">
-        <v>10100</v>
-      </c>
-      <c r="H13">
-        <v>12</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="G13" s="6">
+        <v>10070</v>
+      </c>
+      <c r="H13" s="7">
+        <v>12</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -930,54 +943,54 @@
       <c r="B14" s="3">
         <v>162</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5">
         <v>46245</v>
       </c>
       <c r="E14" s="3">
         <v>7485</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>5000</v>
       </c>
-      <c r="H14">
-        <v>12</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="H14" s="7">
+        <v>12</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>1487</v>
+        <v>1440</v>
       </c>
       <c r="B15" s="3">
         <v>162</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
         <v>46206</v>
       </c>
       <c r="E15" s="3">
         <v>17075</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="F15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="6">
         <v>1340</v>
       </c>
-      <c r="H15">
-        <v>12</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="H15" s="7">
+        <v>12</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -988,54 +1001,54 @@
       <c r="B16" s="3">
         <v>162</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="4">
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="5">
         <v>46204</v>
       </c>
       <c r="E16" s="3">
         <v>7484</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="7">
-        <v>10000</v>
-      </c>
-      <c r="H16">
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="G16" s="6">
+        <v>10100</v>
+      </c>
+      <c r="H16" s="7">
+        <v>12</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B17" s="3">
         <v>162</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5">
         <v>46252</v>
       </c>
       <c r="E17" s="3">
-        <v>10090</v>
-      </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="7">
-        <v>3000</v>
-      </c>
-      <c r="H17">
-        <v>12</v>
-      </c>
-      <c r="I17" t="s">
+        <v>7484</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="6">
+        <v>20000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>12</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1046,175 +1059,262 @@
       <c r="B18" s="3">
         <v>162</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="4">
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="5">
         <v>46252</v>
       </c>
       <c r="E18" s="3">
-        <v>7484</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="7">
-        <v>20000</v>
-      </c>
-      <c r="H18">
-        <v>12</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
+        <v>4413</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>12</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="B19" s="3">
         <v>162</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="5">
         <v>46252</v>
       </c>
       <c r="E19" s="3">
-        <v>4413</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="7">
-        <v>3000</v>
-      </c>
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
+        <v>30189</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="6">
+        <v>7000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>12</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>1668</v>
+        <v>1697</v>
       </c>
       <c r="B20" s="3">
         <v>162</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="4">
-        <v>46252</v>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46261</v>
       </c>
       <c r="E20" s="3">
-        <v>30189</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="7">
-        <v>7000</v>
-      </c>
-      <c r="H20">
-        <v>12</v>
-      </c>
-      <c r="I20" t="s">
-        <v>20</v>
+        <v>17075</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>12</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>1487</v>
+        <v>1666</v>
       </c>
       <c r="B21" s="3">
         <v>162</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="4">
-        <v>46261</v>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46252</v>
       </c>
       <c r="E21" s="3">
-        <v>17075</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="7">
-        <v>2000</v>
-      </c>
-      <c r="H21">
-        <v>12</v>
-      </c>
-      <c r="I21" t="s">
+        <v>10090</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>12</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>1666</v>
+        <v>1697</v>
       </c>
       <c r="B22" s="3">
         <v>162</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="4">
-        <v>46252</v>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46262</v>
       </c>
       <c r="E22" s="3">
-        <v>10090</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="7">
+        <v>9000</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>12</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>1710</v>
+      </c>
+      <c r="B23" s="3">
+        <v>162</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>46266</v>
+      </c>
+      <c r="E23" s="9">
+        <v>13150</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="6">
         <v>3000</v>
       </c>
-      <c r="H22">
-        <v>12</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>1697</v>
-      </c>
-      <c r="B23" s="3">
-        <v>162</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="7">
-        <v>1000</v>
-      </c>
-      <c r="H23">
-        <v>12</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="H23" s="7">
+        <v>12</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>1717</v>
+      </c>
+      <c r="B24" s="3">
+        <v>162</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46266</v>
+      </c>
+      <c r="E24" s="9">
+        <v>17075</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>12</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
+        <v>1685</v>
+      </c>
+      <c r="B25" s="3">
+        <v>162</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="5">
+        <v>46267</v>
+      </c>
+      <c r="E25" s="9">
+        <v>12514</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="6">
+        <v>6000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>12</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>1685</v>
+      </c>
+      <c r="B26" s="3">
+        <v>162</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46268</v>
+      </c>
+      <c r="E26" s="9">
+        <v>12515</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="6">
+        <v>6000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>12</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0E91B54-7ABF-4411-BFAB-BA25568A32F5}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A486A2-530E-4CE8-AA68-275602039FA2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="27">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>TRANSFER 99-5-4 PARCIAL FOIL - SILVER</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FILM - GRAPHITE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
   </si>
 </sst>
 </file>
@@ -223,6 +229,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -545,7 +555,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -590,7 +600,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1467</v>
+        <v>1440</v>
       </c>
       <c r="B2" s="3">
         <v>162</v>
@@ -599,27 +609,27 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="E2" s="3">
-        <v>4413</v>
+        <v>17075</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" s="6">
-        <v>3000</v>
+        <v>1340</v>
       </c>
       <c r="H2" s="7">
         <v>12</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B3" s="3">
         <v>162</v>
@@ -631,24 +641,24 @@
         <v>46204</v>
       </c>
       <c r="E3" s="3">
-        <v>10090</v>
+        <v>4413</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" s="6">
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="H3" s="7">
         <v>12</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="B4" s="3">
         <v>162</v>
@@ -660,24 +670,24 @@
         <v>46204</v>
       </c>
       <c r="E4" s="3">
-        <v>12515</v>
+        <v>7484</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" s="6">
-        <v>6480</v>
+        <v>10100</v>
       </c>
       <c r="H4" s="7">
         <v>12</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1487</v>
+        <v>1469</v>
       </c>
       <c r="B5" s="3">
         <v>162</v>
@@ -686,16 +696,16 @@
         <v>6</v>
       </c>
       <c r="D5" s="5">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="E5" s="3">
-        <v>17075</v>
+        <v>10090</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" s="6">
-        <v>4230</v>
+        <v>3250</v>
       </c>
       <c r="H5" s="7">
         <v>12</v>
@@ -706,7 +716,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>1565</v>
+        <v>1470</v>
       </c>
       <c r="B6" s="3">
         <v>162</v>
@@ -715,27 +725,27 @@
         <v>6</v>
       </c>
       <c r="D6" s="5">
-        <v>46225</v>
+        <v>46204</v>
       </c>
       <c r="E6" s="3">
-        <v>7484</v>
+        <v>12515</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6" s="6">
-        <v>8800</v>
+        <v>6480</v>
       </c>
       <c r="H6" s="7">
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>1565</v>
+        <v>1487</v>
       </c>
       <c r="B7" s="3">
         <v>162</v>
@@ -744,16 +754,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="5">
-        <v>46225</v>
+        <v>46206</v>
       </c>
       <c r="E7" s="3">
-        <v>7485</v>
+        <v>17075</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7" s="6">
-        <v>6000</v>
+        <v>4230</v>
       </c>
       <c r="H7" s="7">
         <v>12</v>
@@ -776,13 +786,13 @@
         <v>46225</v>
       </c>
       <c r="E8" s="3">
-        <v>10090</v>
+        <v>7484</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="6">
-        <v>3200</v>
+        <v>8800</v>
       </c>
       <c r="H8" s="7">
         <v>12</v>
@@ -805,13 +815,13 @@
         <v>46225</v>
       </c>
       <c r="E9" s="3">
-        <v>17076</v>
+        <v>7485</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G9" s="6">
-        <v>3070</v>
+        <v>6000</v>
       </c>
       <c r="H9" s="7">
         <v>12</v>
@@ -822,7 +832,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>1582</v>
+        <v>1565</v>
       </c>
       <c r="B10" s="3">
         <v>162</v>
@@ -831,16 +841,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="5">
-        <v>46233</v>
+        <v>46225</v>
       </c>
       <c r="E10" s="3">
-        <v>7484</v>
+        <v>10090</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="6">
-        <v>9000</v>
+        <v>3200</v>
       </c>
       <c r="H10" s="7">
         <v>12</v>
@@ -851,7 +861,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>1582</v>
+        <v>1565</v>
       </c>
       <c r="B11" s="3">
         <v>162</v>
@@ -860,16 +870,16 @@
         <v>6</v>
       </c>
       <c r="D11" s="5">
-        <v>46233</v>
+        <v>46225</v>
       </c>
       <c r="E11" s="3">
-        <v>7485</v>
+        <v>17076</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G11" s="6">
-        <v>3000</v>
+        <v>3070</v>
       </c>
       <c r="H11" s="7">
         <v>12</v>
@@ -892,13 +902,13 @@
         <v>46233</v>
       </c>
       <c r="E12" s="3">
-        <v>10090</v>
+        <v>7484</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="6">
-        <v>3100</v>
+        <v>9000</v>
       </c>
       <c r="H12" s="7">
         <v>12</v>
@@ -909,7 +919,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>1602</v>
+        <v>1582</v>
       </c>
       <c r="B13" s="3">
         <v>162</v>
@@ -918,16 +928,16 @@
         <v>6</v>
       </c>
       <c r="D13" s="5">
-        <v>46239</v>
+        <v>46233</v>
       </c>
       <c r="E13" s="3">
-        <v>7484</v>
+        <v>7485</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="6">
-        <v>10070</v>
+        <v>3000</v>
       </c>
       <c r="H13" s="7">
         <v>12</v>
@@ -938,7 +948,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>1633</v>
+        <v>1602</v>
       </c>
       <c r="B14" s="3">
         <v>162</v>
@@ -947,16 +957,16 @@
         <v>6</v>
       </c>
       <c r="D14" s="5">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="E14" s="3">
-        <v>7485</v>
+        <v>7484</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G14" s="6">
-        <v>5000</v>
+        <v>10070</v>
       </c>
       <c r="H14" s="7">
         <v>12</v>
@@ -967,7 +977,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>1440</v>
+        <v>1633</v>
       </c>
       <c r="B15" s="3">
         <v>162</v>
@@ -976,16 +986,16 @@
         <v>6</v>
       </c>
       <c r="D15" s="5">
-        <v>46206</v>
+        <v>46245</v>
       </c>
       <c r="E15" s="3">
-        <v>17075</v>
+        <v>7485</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G15" s="6">
-        <v>1340</v>
+        <v>5000</v>
       </c>
       <c r="H15" s="7">
         <v>12</v>
@@ -996,7 +1006,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>1468</v>
+        <v>1665</v>
       </c>
       <c r="B16" s="3">
         <v>162</v>
@@ -1005,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="5">
-        <v>46204</v>
+        <v>46252</v>
       </c>
       <c r="E16" s="3">
         <v>7484</v>
@@ -1014,7 +1024,7 @@
         <v>9</v>
       </c>
       <c r="G16" s="6">
-        <v>10100</v>
+        <v>17300</v>
       </c>
       <c r="H16" s="7">
         <v>12</v>
@@ -1037,24 +1047,24 @@
         <v>46252</v>
       </c>
       <c r="E17" s="3">
-        <v>7484</v>
+        <v>4413</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="6">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="H17" s="7">
         <v>12</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B18" s="3">
         <v>162</v>
@@ -1066,19 +1076,19 @@
         <v>46252</v>
       </c>
       <c r="E18" s="3">
-        <v>4413</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>8</v>
+        <v>10090</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="G18" s="6">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H18" s="7">
         <v>12</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1111,8 +1121,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>1697</v>
+      <c r="A20" s="9">
+        <v>1685</v>
       </c>
       <c r="B20" s="3">
         <v>162</v>
@@ -1121,27 +1131,27 @@
         <v>6</v>
       </c>
       <c r="D20" s="5">
-        <v>46261</v>
-      </c>
-      <c r="E20" s="3">
-        <v>17075</v>
+        <v>46267</v>
+      </c>
+      <c r="E20" s="9">
+        <v>12514</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G20" s="6">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H20" s="7">
         <v>12</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>1666</v>
+      <c r="A21" s="9">
+        <v>1685</v>
       </c>
       <c r="B21" s="3">
         <v>162</v>
@@ -1150,22 +1160,22 @@
         <v>6</v>
       </c>
       <c r="D21" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E21" s="3">
-        <v>10090</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>10</v>
+        <v>46268</v>
+      </c>
+      <c r="E21" s="9">
+        <v>12515</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="G21" s="6">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H21" s="7">
         <v>12</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1179,46 +1189,46 @@
         <v>6</v>
       </c>
       <c r="D22" s="5">
+        <v>46261</v>
+      </c>
+      <c r="E22" s="3">
+        <v>17075</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>12</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>1697</v>
+      </c>
+      <c r="B23" s="3">
+        <v>162</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
         <v>46262</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E23" s="3">
         <v>9000</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G23" s="6">
         <v>1000</v>
       </c>
-      <c r="H22" s="7">
-        <v>12</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>1710</v>
-      </c>
-      <c r="B23" s="3">
-        <v>162</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E23" s="9">
-        <v>13150</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="6">
-        <v>3000</v>
-      </c>
       <c r="H23" s="7">
         <v>12</v>
       </c>
@@ -1227,8 +1237,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>1717</v>
+      <c r="A24" s="3">
+        <v>1697</v>
       </c>
       <c r="B24" s="3">
         <v>162</v>
@@ -1237,13 +1247,13 @@
         <v>6</v>
       </c>
       <c r="D24" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E24" s="9">
-        <v>17075</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>12</v>
+        <v>46263</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10090</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="G24" s="6">
         <v>3000</v>
@@ -1257,7 +1267,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
-        <v>1685</v>
+        <v>1710</v>
       </c>
       <c r="B25" s="3">
         <v>162</v>
@@ -1266,27 +1276,27 @@
         <v>6</v>
       </c>
       <c r="D25" s="5">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="E25" s="9">
-        <v>12514</v>
+        <v>13150</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G25" s="6">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H25" s="7">
         <v>12</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
-        <v>1685</v>
+        <v>1717</v>
       </c>
       <c r="B26" s="3">
         <v>162</v>
@@ -1295,26 +1305,233 @@
         <v>6</v>
       </c>
       <c r="D26" s="5">
+        <v>46266</v>
+      </c>
+      <c r="E26" s="9">
+        <v>17075</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>12</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="9">
+        <v>1792</v>
+      </c>
+      <c r="B27" s="3">
+        <v>162</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5">
+        <v>46267</v>
+      </c>
+      <c r="E27" s="9">
+        <v>7484</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="6">
+        <v>20000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>12</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B28" s="3">
+        <v>162</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="5">
         <v>46268</v>
       </c>
-      <c r="E26" s="9">
-        <v>12515</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="6">
-        <v>6000</v>
-      </c>
-      <c r="H26" s="7">
-        <v>12</v>
-      </c>
-      <c r="I26" s="7" t="s">
+      <c r="E28" s="9">
+        <v>9000</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>12</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B29" s="3">
+        <v>162</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="5">
+        <v>46269</v>
+      </c>
+      <c r="E29" s="9">
+        <v>10090</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>12</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B30" s="3">
+        <v>162</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46270</v>
+      </c>
+      <c r="E30" s="9">
+        <v>12517</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>12</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B31" s="3">
+        <v>162</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>46271</v>
+      </c>
+      <c r="E31" s="9">
+        <v>12518</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>12</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B32" s="3">
+        <v>162</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46272</v>
+      </c>
+      <c r="E32" s="9">
+        <v>17075</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>12</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>1770</v>
+      </c>
+      <c r="B33" s="3">
+        <v>162</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>46273</v>
+      </c>
+      <c r="E33" s="9">
+        <v>7484</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="6">
+        <v>5000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>12</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I27" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
+      <sortCondition ref="A1:A26"/>
+    </sortState>
+  </autoFilter>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="9999" orientation="landscape"/>

--- a/data-source/COMPRATRANSFER.xlsx
+++ b/data-source/COMPRATRANSFER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/TRANSFER-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="8_{77FF3A89-80B9-407D-BABF-BDBB720C2313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36A486A2-530E-4CE8-AA68-275602039FA2}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="14_{42D477D6-2A30-45A0-ABAB-3676C37B368B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176C7177-5918-4717-A480-C295F4F3D017}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Plan1!$A$1:$I$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Plan1!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>TRANSFER 99-5-4 PARCIAL FILM - ROSE GOLD</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - GRAPHITE</t>
+  </si>
+  <si>
+    <t>TRANSFER 99-5-4 PARCIAL FOIL - ROSE GOLD</t>
   </si>
 </sst>
 </file>
@@ -158,7 +164,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -210,9 +216,6 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -229,10 +232,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -555,7 +554,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -600,7 +599,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>1440</v>
+        <v>1565</v>
       </c>
       <c r="B2" s="3">
         <v>162</v>
@@ -609,16 +608,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>46206</v>
+        <v>46225</v>
       </c>
       <c r="E2" s="3">
-        <v>17075</v>
+        <v>7484</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2" s="6">
-        <v>1340</v>
+        <v>8800</v>
       </c>
       <c r="H2" s="7">
         <v>12</v>
@@ -629,7 +628,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>1467</v>
+        <v>1565</v>
       </c>
       <c r="B3" s="3">
         <v>162</v>
@@ -638,27 +637,27 @@
         <v>6</v>
       </c>
       <c r="D3" s="5">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="E3" s="3">
-        <v>4413</v>
+        <v>7485</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="6">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H3" s="7">
         <v>12</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>1468</v>
+        <v>1565</v>
       </c>
       <c r="B4" s="3">
         <v>162</v>
@@ -667,16 +666,16 @@
         <v>6</v>
       </c>
       <c r="D4" s="5">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="E4" s="3">
-        <v>7484</v>
+        <v>10090</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="6">
-        <v>10100</v>
+        <v>3200</v>
       </c>
       <c r="H4" s="7">
         <v>12</v>
@@ -687,7 +686,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>1469</v>
+        <v>1565</v>
       </c>
       <c r="B5" s="3">
         <v>162</v>
@@ -696,16 +695,16 @@
         <v>6</v>
       </c>
       <c r="D5" s="5">
-        <v>46204</v>
+        <v>46225</v>
       </c>
       <c r="E5" s="3">
-        <v>10090</v>
+        <v>17076</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" s="6">
-        <v>3250</v>
+        <v>3070</v>
       </c>
       <c r="H5" s="7">
         <v>12</v>
@@ -716,7 +715,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>1470</v>
+        <v>1582</v>
       </c>
       <c r="B6" s="3">
         <v>162</v>
@@ -725,27 +724,27 @@
         <v>6</v>
       </c>
       <c r="D6" s="5">
-        <v>46204</v>
+        <v>46233</v>
       </c>
       <c r="E6" s="3">
-        <v>12515</v>
+        <v>7484</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" s="6">
-        <v>6480</v>
+        <v>9000</v>
       </c>
       <c r="H6" s="7">
         <v>12</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>1487</v>
+        <v>1582</v>
       </c>
       <c r="B7" s="3">
         <v>162</v>
@@ -754,16 +753,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="5">
-        <v>46206</v>
+        <v>46233</v>
       </c>
       <c r="E7" s="3">
-        <v>17075</v>
+        <v>7485</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G7" s="6">
-        <v>4230</v>
+        <v>3000</v>
       </c>
       <c r="H7" s="7">
         <v>12</v>
@@ -774,7 +773,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>1565</v>
+        <v>1602</v>
       </c>
       <c r="B8" s="3">
         <v>162</v>
@@ -783,7 +782,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="5">
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="E8" s="3">
         <v>7484</v>
@@ -792,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="6">
-        <v>8800</v>
+        <v>10070</v>
       </c>
       <c r="H8" s="7">
         <v>12</v>
@@ -803,7 +802,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>1565</v>
+        <v>1633</v>
       </c>
       <c r="B9" s="3">
         <v>162</v>
@@ -812,7 +811,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="5">
-        <v>46225</v>
+        <v>46245</v>
       </c>
       <c r="E9" s="3">
         <v>7485</v>
@@ -821,7 +820,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="6">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H9" s="7">
         <v>12</v>
@@ -832,7 +831,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>1565</v>
+        <v>1665</v>
       </c>
       <c r="B10" s="3">
         <v>162</v>
@@ -841,16 +840,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="5">
-        <v>46225</v>
+        <v>46252</v>
       </c>
       <c r="E10" s="3">
-        <v>10090</v>
+        <v>7484</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="6">
-        <v>3200</v>
+        <v>17300</v>
       </c>
       <c r="H10" s="7">
         <v>12</v>
@@ -861,7 +860,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>1565</v>
+        <v>1665</v>
       </c>
       <c r="B11" s="3">
         <v>162</v>
@@ -870,27 +869,27 @@
         <v>6</v>
       </c>
       <c r="D11" s="5">
-        <v>46225</v>
+        <v>46252</v>
       </c>
       <c r="E11" s="3">
-        <v>17076</v>
+        <v>4413</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G11" s="6">
-        <v>3070</v>
+        <v>3000</v>
       </c>
       <c r="H11" s="7">
         <v>12</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>1582</v>
+        <v>1668</v>
       </c>
       <c r="B12" s="3">
         <v>162</v>
@@ -899,230 +898,230 @@
         <v>6</v>
       </c>
       <c r="D12" s="5">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="E12" s="3">
+        <v>30189</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="6">
+        <v>6500</v>
+      </c>
+      <c r="H12" s="7">
+        <v>12</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1685</v>
+      </c>
+      <c r="B13" s="3">
+        <v>162</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>46267</v>
+      </c>
+      <c r="E13" s="8">
+        <v>12514</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="6">
+        <v>6000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>12</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>1685</v>
+      </c>
+      <c r="B14" s="3">
+        <v>162</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46268</v>
+      </c>
+      <c r="E14" s="8">
+        <v>12515</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="6">
+        <v>6700</v>
+      </c>
+      <c r="H14" s="7">
+        <v>12</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>1710</v>
+      </c>
+      <c r="B15" s="3">
+        <v>162</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46266</v>
+      </c>
+      <c r="E15" s="8">
+        <v>13150</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>12</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>1717</v>
+      </c>
+      <c r="B16" s="3">
+        <v>162</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46266</v>
+      </c>
+      <c r="E16" s="8">
+        <v>17075</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>12</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>1792</v>
+      </c>
+      <c r="B17" s="3">
+        <v>162</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5">
+        <v>46267</v>
+      </c>
+      <c r="E17" s="8">
         <v>7484</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G17" s="6">
+        <v>20000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>12</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B18" s="3">
+        <v>162</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46268</v>
+      </c>
+      <c r="E18" s="8">
         <v>9000</v>
       </c>
-      <c r="H12" s="7">
-        <v>12</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>1582</v>
-      </c>
-      <c r="B13" s="3">
-        <v>162</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>46233</v>
-      </c>
-      <c r="E13" s="3">
-        <v>7485</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H13" s="7">
-        <v>12</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>1602</v>
-      </c>
-      <c r="B14" s="3">
-        <v>162</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46239</v>
-      </c>
-      <c r="E14" s="3">
-        <v>7484</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="6">
-        <v>10070</v>
-      </c>
-      <c r="H14" s="7">
-        <v>12</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>1633</v>
-      </c>
-      <c r="B15" s="3">
-        <v>162</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="5">
-        <v>46245</v>
-      </c>
-      <c r="E15" s="3">
-        <v>7485</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="6">
-        <v>5000</v>
-      </c>
-      <c r="H15" s="7">
-        <v>12</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>1665</v>
-      </c>
-      <c r="B16" s="3">
-        <v>162</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E16" s="3">
-        <v>7484</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="6">
-        <v>17300</v>
-      </c>
-      <c r="H16" s="7">
-        <v>12</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>1665</v>
-      </c>
-      <c r="B17" s="3">
-        <v>162</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4413</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H17" s="7">
-        <v>12</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>1666</v>
-      </c>
-      <c r="B18" s="3">
-        <v>162</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="F18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>12</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>1770</v>
+      </c>
+      <c r="B19" s="3">
+        <v>162</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46269</v>
+      </c>
+      <c r="E19" s="8">
         <v>10090</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="6">
-        <v>3100</v>
-      </c>
-      <c r="H18" s="7">
-        <v>12</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>1668</v>
-      </c>
-      <c r="B19" s="3">
-        <v>162</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>46252</v>
-      </c>
-      <c r="E19" s="3">
-        <v>30189</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="G19" s="6">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="H19" s="7">
         <v>12</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>1685</v>
+      <c r="A20" s="8">
+        <v>1770</v>
       </c>
       <c r="B20" s="3">
         <v>162</v>
@@ -1131,16 +1130,16 @@
         <v>6</v>
       </c>
       <c r="D20" s="5">
-        <v>46267</v>
-      </c>
-      <c r="E20" s="9">
-        <v>12514</v>
+        <v>46270</v>
+      </c>
+      <c r="E20" s="8">
+        <v>12517</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="6">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="7">
         <v>12</v>
@@ -1150,8 +1149,8 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>1685</v>
+      <c r="A21" s="8">
+        <v>1770</v>
       </c>
       <c r="B21" s="3">
         <v>162</v>
@@ -1160,16 +1159,16 @@
         <v>6</v>
       </c>
       <c r="D21" s="5">
-        <v>46268</v>
-      </c>
-      <c r="E21" s="9">
-        <v>12515</v>
+        <v>46271</v>
+      </c>
+      <c r="E21" s="8">
+        <v>12518</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G21" s="6">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="7">
         <v>12</v>
@@ -1179,8 +1178,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>1697</v>
+      <c r="A22" s="8">
+        <v>1770</v>
       </c>
       <c r="B22" s="3">
         <v>162</v>
@@ -1189,9 +1188,9 @@
         <v>6</v>
       </c>
       <c r="D22" s="5">
-        <v>46261</v>
-      </c>
-      <c r="E22" s="3">
+        <v>46272</v>
+      </c>
+      <c r="E22" s="8">
         <v>17075</v>
       </c>
       <c r="F22" s="4" t="s">
@@ -1208,8 +1207,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>1697</v>
+      <c r="A23" s="8">
+        <v>1840</v>
       </c>
       <c r="B23" s="3">
         <v>162</v>
@@ -1218,27 +1217,27 @@
         <v>6</v>
       </c>
       <c r="D23" s="5">
-        <v>46262</v>
-      </c>
-      <c r="E23" s="3">
-        <v>9000</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>22</v>
+        <v>46288</v>
+      </c>
+      <c r="E23" s="8">
+        <v>12517</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="G23" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="7">
         <v>12</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>1697</v>
+      <c r="A24" s="8">
+        <v>1840</v>
       </c>
       <c r="B24" s="3">
         <v>162</v>
@@ -1247,289 +1246,28 @@
         <v>6</v>
       </c>
       <c r="D24" s="5">
-        <v>46263</v>
-      </c>
-      <c r="E24" s="3">
-        <v>10090</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>22</v>
+        <v>46288</v>
+      </c>
+      <c r="E24" s="8">
+        <v>12518</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="G24" s="6">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H24" s="7">
         <v>12</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="9">
-        <v>1710</v>
-      </c>
-      <c r="B25" s="3">
-        <v>162</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E25" s="9">
-        <v>13150</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H25" s="7">
-        <v>12</v>
-      </c>
-      <c r="I25" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="9">
-        <v>1717</v>
-      </c>
-      <c r="B26" s="3">
-        <v>162</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46266</v>
-      </c>
-      <c r="E26" s="9">
-        <v>17075</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H26" s="7">
-        <v>12</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="9">
-        <v>1792</v>
-      </c>
-      <c r="B27" s="3">
-        <v>162</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="5">
-        <v>46267</v>
-      </c>
-      <c r="E27" s="9">
-        <v>7484</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G27" s="6">
-        <v>20000</v>
-      </c>
-      <c r="H27" s="7">
-        <v>12</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B28" s="3">
-        <v>162</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="5">
-        <v>46268</v>
-      </c>
-      <c r="E28" s="9">
-        <v>9000</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H28" s="7">
-        <v>12</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B29" s="3">
-        <v>162</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="5">
-        <v>46269</v>
-      </c>
-      <c r="E29" s="9">
-        <v>10090</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H29" s="7">
-        <v>12</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B30" s="3">
-        <v>162</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46270</v>
-      </c>
-      <c r="E30" s="9">
-        <v>12517</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H30" s="7">
-        <v>12</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B31" s="3">
-        <v>162</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="5">
-        <v>46271</v>
-      </c>
-      <c r="E31" s="9">
-        <v>12518</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H31" s="7">
-        <v>12</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B32" s="3">
-        <v>162</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46272</v>
-      </c>
-      <c r="E32" s="9">
-        <v>17075</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H32" s="7">
-        <v>12</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="9">
-        <v>1770</v>
-      </c>
-      <c r="B33" s="3">
-        <v>162</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="5">
-        <v>46273</v>
-      </c>
-      <c r="E33" s="9">
-        <v>7484</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="6">
-        <v>5000</v>
-      </c>
-      <c r="H33" s="7">
-        <v>12</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I27" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I26">
-      <sortCondition ref="A1:A26"/>
+  <autoFilter ref="A1:I17" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I16">
+      <sortCondition ref="A1:A16"/>
     </sortState>
   </autoFilter>
   <printOptions gridLines="1"/>
